--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1717-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1717-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA2620CC-03B5-40B6-9E97-362F7B64808D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D081D186-602A-4D62-890B-71F1B4BBDB53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{C64432D7-AD00-4830-B1A4-5EC8DFBE00AD}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{569ACA56-9095-4A1C-B613-B538D8A46BD1}"/>
   </bookViews>
   <sheets>
     <sheet name="1717-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1580,26 +1580,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DF75BC6-F24F-4612-90C5-BED86E32A648}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0908AA7E-88B6-4F6C-A918-7E96DC665104}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="8" width="6.625" customWidth="1"/>
-    <col min="9" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="15" width="6.625" customWidth="1"/>
-    <col min="16" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1633,7 +1632,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1669,7 +1668,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1721,7 +1720,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1789,7 +1788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="39">
         <v>2021</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>5.12</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>2020</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="39">
         <v>2019</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>6.93</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2018</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>3.86</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="39">
         <v>2017</v>
       </c>
@@ -2365,7 +2364,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2016</v>
       </c>
@@ -2437,7 +2436,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="39">
         <v>2015</v>
       </c>
@@ -2509,7 +2508,7 @@
         <v>7.52</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>2014</v>
       </c>
@@ -2581,7 +2580,7 @@
         <v>6.62</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="39">
         <v>2013</v>
       </c>
@@ -2653,7 +2652,7 @@
         <v>6.16</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2012</v>
       </c>
@@ -2725,7 +2724,7 @@
         <v>4.8899999999999997</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="39">
         <v>2011</v>
       </c>
@@ -2797,7 +2796,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2010</v>
       </c>
@@ -2869,7 +2868,7 @@
         <v>9.57</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="41">
         <v>2009</v>
       </c>
@@ -2941,7 +2940,7 @@
         <v>9.31</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="43"/>
       <c r="B21" s="44"/>
       <c r="C21" s="18" t="s">
@@ -2969,7 +2968,7 @@
       <c r="W21" s="50"/>
       <c r="X21" s="46"/>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="51">
         <v>2008</v>
       </c>
@@ -3041,7 +3040,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="53"/>
       <c r="B23" s="54"/>
       <c r="C23" s="20" t="s">
@@ -3069,7 +3068,7 @@
       <c r="W23" s="60"/>
       <c r="X23" s="56"/>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="41">
         <v>2007</v>
       </c>
@@ -3141,7 +3140,7 @@
         <v>17.3</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="43"/>
       <c r="B25" s="44"/>
       <c r="C25" s="18" t="s">
@@ -3169,7 +3168,7 @@
       <c r="W25" s="50"/>
       <c r="X25" s="46"/>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2006</v>
       </c>
@@ -3241,7 +3240,7 @@
         <v>7.87</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2005</v>
       </c>
@@ -3313,7 +3312,7 @@
         <v>8.8000000000000007</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="51">
         <v>2004</v>
       </c>
@@ -3385,7 +3384,7 @@
         <v>9.76</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="53"/>
       <c r="B29" s="54"/>
       <c r="C29" s="20" t="s">
@@ -3413,7 +3412,7 @@
       <c r="W29" s="60"/>
       <c r="X29" s="56"/>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="39">
         <v>2003</v>
       </c>
@@ -3485,7 +3484,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2002</v>
       </c>
@@ -3557,7 +3556,7 @@
         <v>8.64</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="41">
         <v>2001</v>
       </c>
@@ -3629,7 +3628,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="43"/>
       <c r="B33" s="44"/>
       <c r="C33" s="18" t="s">
@@ -3657,7 +3656,7 @@
       <c r="W33" s="50"/>
       <c r="X33" s="46"/>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2000</v>
       </c>
@@ -3729,7 +3728,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>1999</v>
       </c>
@@ -3801,7 +3800,7 @@
         <v>14.9</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1998</v>
       </c>
@@ -3873,7 +3872,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>1997</v>
       </c>
@@ -3945,7 +3944,7 @@
         <v>7.33</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1996</v>
       </c>
@@ -4017,7 +4016,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1995</v>
       </c>
@@ -4089,7 +4088,7 @@
         <v>5.71</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1994</v>
       </c>
@@ -4161,7 +4160,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1993</v>
       </c>
@@ -4233,7 +4232,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1992</v>
       </c>
@@ -4305,7 +4304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="41">
         <v>1991</v>
       </c>
@@ -4377,7 +4376,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="43"/>
       <c r="B44" s="44"/>
       <c r="C44" s="18" t="s">
@@ -4405,7 +4404,7 @@
       <c r="W44" s="50"/>
       <c r="X44" s="46"/>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
         <v>62</v>
       </c>
